--- a/questionnaire_templates/047_refresher_pre_test_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/047_refresher_pre_test_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is a series of questions to help us understand your current level of knowledge and confidence in the organization.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,7 +570,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,10 +578,14 @@
           <t>What is your role in the organization?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please be specific about your job title and responsibilities.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,58 +597,62 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1_answer</t>
+          <t>question1_answer</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is your role in the organization?</t>
+          <t>How long have you been in the role?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How long have you been in the role?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What type of training have you received?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select all relevant options</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_2_answer</t>
+          <t>section2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How long have you been in the role?</t>
+          <t>Section 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +670,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What type of training have you received?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How do you feel about your current level of knowledge?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select one of the options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +697,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3_answer</t>
+          <t>question4_answer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What type of training have you received?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How do you feel about your current level of confidence?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please describe your confidence level</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +724,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>section2</t>
+          <t>section3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Section 2</t>
+          <t>Section 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +747,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How do you feel about your current level of knowledge?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you feel like you need additional training?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select one of the options</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +774,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_4_answer</t>
+          <t>question5_answer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How do you feel about your current level of knowledge?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What type of training do you need?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please specify the type of training</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,18 +801,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How do you feel about your current level of confidence?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Would you like to receive more information about upcoming training events?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select one of the options</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,61 +828,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_5_answer</t>
+          <t>question6_answer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How do you feel about your current level of confidence?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Do you need help with any other specific topic?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please specify the topic</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>section3</t>
+          <t>question7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Section 3</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Do you have any other comments or suggestions?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide your feedback</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Do you feel like you need additional training?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please add your name and date</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,17 +904,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_6_answer</t>
+          <t>question8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Do you feel like you need additional training?</t>
+          <t>Question8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,20 +927,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question8_answer</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What type of training do you need?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Question8 Answer</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please specify the topic</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,177 +959,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_7_answer</t>
+          <t>question9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What type of training do you need?</t>
+          <t>Question9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Would you like to receive more information about upcoming training events?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_8_answer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Would you like to receive more information about upcoming training events?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you need help with any other specific topic?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_9_answer</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you need help with any other specific topic?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any other comments or suggestions?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_10_answer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you have any other comments or suggestions?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +985,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1160,338 +1047,355 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>team_leader</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Team Leader</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>section2_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>technical_training</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Technical Training</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>section2_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>soft_skills_training</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Soft Skills Training</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>leadership_training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Leadership Training</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>section2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>section2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>section3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>section3_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>section3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>section3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question6_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_9_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question8_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
